--- a/data/trans_dic/IP31KM12_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM12_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,31; 100,0</t>
+          <t>97,41; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>97,23; 100,0</t>
+          <t>96,38; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,72; 99,74</t>
+          <t>97,79; 99,84</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,8; 97,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,07; 98,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,62; 99,0</t>
+          <t>94,46; 98,93</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,41; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>93,05; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,49; 100,0</t>
+          <t>96,74; 100,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,46; 99,3</t>
+          <t>96,16; 99,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96,26; 99,72</t>
+          <t>94,45; 99,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,92; 99,18</t>
+          <t>96,4; 99,02</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>93,01; 98,69</t>
+          <t>96,06; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96,29; 100,0</t>
+          <t>92,65; 98,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95,82; 99,05</t>
+          <t>95,77; 99,06</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,98; 97,83</t>
+          <t>92,18; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91,86; 100,0</t>
+          <t>87,08; 98,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,24; 98,74</t>
+          <t>91,81; 98,65</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,85; 98,07</t>
+          <t>98,18; 99,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>98,3; 99,62</t>
+          <t>95,53; 97,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97,44; 98,71</t>
+          <t>97,38; 98,71</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>150</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>100642</t>
+          <t>120318</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>134088</t>
+          <t>99317</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>234731</t>
+          <t>219635</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97952; 101709</t>
+          <t>118068; 121209</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>131434; 135176</t>
+          <t>96713; 100349</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>231473; 236260</t>
+          <t>216667; 221201</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>131</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>88825</t>
+          <t>89880</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>90817</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>182534</t>
+          <t>180697</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83868; 91447</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>85938; 93611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>177029; 185234</t>
+          <t>175028; 183308</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49374</t>
+          <t>55844</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>51314</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111707</t>
+          <t>107158</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46285; 50089</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>48395; 52010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108478; 112422</t>
+          <t>104341; 107854</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>265</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>211317</t>
+          <t>194418</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>209620</t>
+          <t>172295</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>420938</t>
+          <t>366713</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>205762; 214027</t>
+          <t>189735; 196611</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>204696; 212062</t>
+          <t>166842; 174935</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>415002; 424705</t>
+          <t>360490; 370278</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>165</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>111449</t>
+          <t>144129</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>157915</t>
+          <t>111442</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>269363</t>
+          <t>255571</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>107429; 113997</t>
+          <t>139853; 145586</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153539; 159461</t>
+          <t>106976; 113849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>263476; 272357</t>
+          <t>250011; 258592</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>65074</t>
+          <t>64848</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>67973</t>
+          <t>66383</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133046</t>
+          <t>131232</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>59925; 67397</t>
+          <t>60712; 65863</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63414; 69031</t>
+          <t>61263; 69171</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>127224; 136186</t>
+          <t>125063; 134380</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>875</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>626682</t>
+          <t>669436</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>725637</t>
+          <t>591569</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1352319</t>
+          <t>1261005</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>618379; 632649</t>
+          <t>663419; 672813</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>719882; 729612</t>
+          <t>582965; 597835</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1342294; 1359762</t>
+          <t>1252260; 1269335</t>
         </is>
       </c>
     </row>
